--- a/But_D1_26_27.xlsx
+++ b/But_D1_26_27.xlsx
@@ -717,7 +717,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.42"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="20.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="1" width="7.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="1" width="7.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="36.91"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="13" style="1" width="18"/>
   </cols>
@@ -6219,7 +6219,7 @@
         <v>2</v>
       </c>
       <c r="L133" s="1" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="M133" s="3" t="s">
         <v>22</v>
@@ -6260,7 +6260,7 @@
         <v>3</v>
       </c>
       <c r="L134" s="1" t="s">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="M134" s="3" t="s">
         <v>22</v>

--- a/But_D1_26_27.xlsx
+++ b/But_D1_26_27.xlsx
@@ -709,7 +709,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W1000"/>
@@ -763,7 +763,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -814,7 +814,7 @@
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -865,7 +865,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
@@ -916,7 +916,7 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>1</v>
       </c>
@@ -967,7 +967,7 @@
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>1</v>
       </c>
@@ -1008,7 +1008,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>1</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>1</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>1</v>
       </c>
@@ -1131,7 +1131,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>1</v>
       </c>
@@ -1172,7 +1172,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>1</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>1</v>
       </c>
@@ -1254,7 +1254,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>1</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>1</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>1</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>1</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>1</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>1</v>
       </c>
@@ -1500,7 +1500,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>1</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>1</v>
       </c>
@@ -1787,7 +1787,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>1</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>1</v>
       </c>
@@ -1869,7 +1869,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>1</v>
       </c>
@@ -1910,7 +1910,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>1</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>1</v>
       </c>
@@ -1992,7 +1992,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>1</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>1</v>
       </c>
@@ -2074,7 +2074,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>1</v>
       </c>
@@ -2115,7 +2115,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>1</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>1</v>
       </c>
@@ -2197,7 +2197,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>1</v>
       </c>
@@ -2238,7 +2238,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>1</v>
       </c>
@@ -2279,7 +2279,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>1</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>1</v>
       </c>
@@ -2361,7 +2361,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>1</v>
       </c>
@@ -2402,7 +2402,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>1</v>
       </c>
@@ -2443,7 +2443,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>1</v>
       </c>
@@ -2484,7 +2484,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
         <v>1</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
         <v>1</v>
       </c>
@@ -2566,7 +2566,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
         <v>1</v>
       </c>
@@ -2607,7 +2607,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>1</v>
       </c>
@@ -2648,7 +2648,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
         <v>2</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
         <v>2</v>
       </c>
@@ -2730,7 +2730,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
         <v>2</v>
       </c>
@@ -2771,7 +2771,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
         <v>2</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
         <v>2</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
         <v>2</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
         <v>2</v>
       </c>
@@ -2935,7 +2935,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
         <v>2</v>
       </c>
@@ -2976,7 +2976,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
         <v>2</v>
       </c>
@@ -3017,7 +3017,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
         <v>2</v>
       </c>
@@ -3058,7 +3058,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="n">
         <v>2</v>
       </c>
@@ -3099,7 +3099,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
         <v>2</v>
       </c>
@@ -3140,7 +3140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="n">
         <v>2</v>
       </c>
@@ -3181,7 +3181,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="n">
         <v>2</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="n">
         <v>2</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="n">
         <v>2</v>
       </c>
@@ -3304,7 +3304,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
         <v>2</v>
       </c>
@@ -3427,7 +3427,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
         <v>2</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="67" s="6" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" s="6" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
         <v>2</v>
       </c>
@@ -3519,7 +3519,7 @@
       <c r="V67" s="1"/>
       <c r="W67" s="1"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
         <v>2</v>
       </c>
@@ -3560,7 +3560,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
         <v>2</v>
       </c>
@@ -3601,7 +3601,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
         <v>2</v>
       </c>
@@ -3642,7 +3642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="n">
         <v>2</v>
       </c>
@@ -3683,7 +3683,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="n">
         <v>2</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="n">
         <v>2</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
         <v>2</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
         <v>2</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="n">
         <v>3</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
         <v>3</v>
       </c>
@@ -3929,7 +3929,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
         <v>3</v>
       </c>
@@ -3970,7 +3970,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="n">
         <v>3</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="n">
         <v>3</v>
       </c>
@@ -4052,7 +4052,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="n">
         <v>3</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="n">
         <v>3</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="n">
         <v>3</v>
       </c>
@@ -4175,7 +4175,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="n">
         <v>3</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="n">
         <v>3</v>
       </c>
@@ -4257,7 +4257,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
         <v>3</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="n">
         <v>3</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="n">
         <v>3</v>
       </c>
@@ -4380,7 +4380,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="n">
         <v>3</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="n">
         <v>3</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="n">
         <v>3</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="n">
         <v>3</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="n">
         <v>3</v>
       </c>
@@ -4585,7 +4585,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="n">
         <v>3</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="n">
         <v>3</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="n">
         <v>3</v>
       </c>
@@ -4708,7 +4708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="n">
         <v>3</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="n">
         <v>3</v>
       </c>
@@ -4790,7 +4790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="n">
         <v>3</v>
       </c>
@@ -4831,7 +4831,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="n">
         <v>3</v>
       </c>
@@ -4872,7 +4872,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="n">
         <v>3</v>
       </c>
@@ -4913,7 +4913,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="n">
         <v>3</v>
       </c>
@@ -4954,7 +4954,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="n">
         <v>3</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="n">
         <v>3</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="n">
         <v>3</v>
       </c>
@@ -5077,7 +5077,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="n">
         <v>3</v>
       </c>
@@ -5152,11 +5152,11 @@
       <c r="K107" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="L107" s="1" t="s">
-        <v>43</v>
+      <c r="L107" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="M107" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5282,7 +5282,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="n">
         <v>3</v>
       </c>
@@ -5323,7 +5323,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="n">
         <v>3</v>
       </c>
@@ -5364,7 +5364,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="n">
         <v>3</v>
       </c>
@@ -5405,7 +5405,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="n">
         <v>3</v>
       </c>
@@ -5446,7 +5446,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="n">
         <v>3</v>
       </c>
@@ -5487,7 +5487,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="n">
         <v>3</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="n">
         <v>3</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="n">
         <v>3</v>
       </c>
@@ -5610,7 +5610,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="n">
         <v>3</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="n">
         <v>3</v>
       </c>
@@ -5692,7 +5692,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="n">
         <v>3</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="n">
         <v>3</v>
       </c>
@@ -5774,7 +5774,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="n">
         <v>3</v>
       </c>
@@ -5815,7 +5815,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="n">
         <v>3</v>
       </c>
@@ -5856,7 +5856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="n">
         <v>3</v>
       </c>
@@ -5897,7 +5897,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="n">
         <v>3</v>
       </c>
@@ -5938,7 +5938,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="n">
         <v>3</v>
       </c>
@@ -5979,7 +5979,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="n">
         <v>3</v>
       </c>
@@ -6020,7 +6020,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="129" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="4" t="n">
         <v>4</v>
       </c>
@@ -6061,7 +6061,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="130" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="4" t="n">
         <v>4</v>
       </c>
@@ -6102,7 +6102,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="131" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="4" t="n">
         <v>4</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="132" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="4" t="n">
         <v>4</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="n">
         <v>4</v>
       </c>
@@ -6225,7 +6225,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="1" t="n">
         <v>4</v>
       </c>
@@ -6266,7 +6266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="1" t="n">
         <v>4</v>
       </c>
@@ -6307,7 +6307,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="1" t="n">
         <v>4</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="1" t="n">
         <v>4</v>
       </c>
@@ -6389,7 +6389,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="1" t="n">
         <v>4</v>
       </c>
@@ -6430,7 +6430,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="1" t="n">
         <v>4</v>
       </c>
@@ -6471,7 +6471,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="1" t="n">
         <v>4</v>
       </c>
@@ -6553,7 +6553,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="1" t="n">
         <v>4</v>
       </c>
@@ -6594,7 +6594,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="1" t="n">
         <v>4</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="1" t="n">
         <v>4</v>
       </c>
@@ -6799,7 +6799,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="1" t="n">
         <v>4</v>
       </c>
@@ -6840,7 +6840,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="1" t="n">
         <v>4</v>
       </c>
@@ -6881,7 +6881,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="1" t="n">
         <v>4</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="1" t="n">
         <v>4</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="n">
         <v>4</v>
       </c>
@@ -7004,7 +7004,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="n">
         <v>4</v>
       </c>
@@ -7045,7 +7045,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="n">
         <v>4</v>
       </c>
@@ -7086,7 +7086,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="n">
         <v>4</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="n">
         <v>4</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="n">
         <v>4</v>
       </c>
@@ -7209,7 +7209,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="n">
         <v>4</v>
       </c>
@@ -7250,7 +7250,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="n">
         <v>4</v>
       </c>
@@ -7291,7 +7291,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="n">
         <v>4</v>
       </c>
@@ -7332,7 +7332,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="n">
         <v>4</v>
       </c>
@@ -7373,7 +7373,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="n">
         <v>4</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="n">
         <v>4</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="n">
         <v>4</v>
       </c>
@@ -7496,7 +7496,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="n">
         <v>4</v>
       </c>
@@ -7537,7 +7537,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="n">
         <v>4</v>
       </c>
@@ -7578,7 +7578,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="n">
         <v>4</v>
       </c>
@@ -10119,7 +10119,13 @@
       <c r="M1000" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M167"/>
+  <autoFilter ref="A1:M167">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="PARIS ACASA FUTSAL"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation allowBlank="true" error="Choisir une origine dans la liste." errorStyle="stop" errorTitle="Origine inconnue" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M2:M1000" type="list">
       <formula1>"attaque placée,attaque rapide,transition off,corner,touche off,touche def,coup franc,jet franc,power play,penalty,csc"</formula1>

--- a/But_D1_26_27.xlsx
+++ b/But_D1_26_27.xlsx
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2344" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2419" uniqueCount="130">
   <si>
     <t xml:space="preserve">journee</t>
   </si>
@@ -364,10 +364,16 @@
     <t xml:space="preserve">JULIO MARECO GALEANO</t>
   </si>
   <si>
-    <t xml:space="preserve">CAIO DOS SANTOS</t>
+    <t xml:space="preserve">JAMAL EL BSAHI</t>
   </si>
   <si>
     <t xml:space="preserve">GABRIEL PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IDRISS RAISS EL FENNI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAIO DOS SANTOS</t>
   </si>
   <si>
     <t xml:space="preserve">YOUNESS AHSSEN</t>
@@ -418,13 +424,7 @@
     <t xml:space="preserve">jet franc</t>
   </si>
   <si>
-    <t xml:space="preserve">IDRISS RAISS EL FENNI</t>
-  </si>
-  <si>
     <t xml:space="preserve">touche def</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JAMAL EL BSAHI</t>
   </si>
   <si>
     <t xml:space="preserve">penalty</t>
@@ -746,7 +746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W1000"/>
@@ -797,7 +797,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
@@ -846,7 +846,7 @@
       <c r="V2" s="4"/>
       <c r="W2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
@@ -895,7 +895,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
@@ -944,7 +944,7 @@
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
         <v>1</v>
       </c>
@@ -993,7 +993,7 @@
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>1</v>
       </c>
@@ -1032,7 +1032,7 @@
       </c>
       <c r="M6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>1</v>
       </c>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="M7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>1</v>
       </c>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="M8" s="3"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>1</v>
       </c>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="M9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>1</v>
       </c>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="M10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
         <v>1</v>
       </c>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="M11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
         <v>1</v>
       </c>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="M12" s="3"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="n">
         <v>1</v>
       </c>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="M13" s="3"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="n">
         <v>1</v>
       </c>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>1</v>
       </c>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="M15" s="3"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="n">
         <v>1</v>
       </c>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="M16" s="3"/>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="n">
         <v>1</v>
       </c>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="n">
         <v>1</v>
       </c>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="M18" s="3"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="n">
         <v>1</v>
       </c>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="M19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>1</v>
       </c>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="M20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>1</v>
       </c>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="M21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>1</v>
       </c>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="M22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>1</v>
       </c>
@@ -1695,7 +1695,7 @@
       </c>
       <c r="M23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>1</v>
       </c>
@@ -1734,7 +1734,7 @@
       </c>
       <c r="M24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>1</v>
       </c>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="M25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="n">
         <v>1</v>
       </c>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="M26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="n">
         <v>1</v>
       </c>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="M27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="n">
         <v>1</v>
       </c>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="M28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="n">
         <v>1</v>
       </c>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="M29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="n">
         <v>1</v>
       </c>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="M30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="n">
         <v>1</v>
       </c>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="M31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="n">
         <v>1</v>
       </c>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="M32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="n">
         <v>1</v>
       </c>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="M33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="n">
         <v>1</v>
       </c>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="M34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="n">
         <v>1</v>
       </c>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="M35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="n">
         <v>1</v>
       </c>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="M36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="n">
         <v>1</v>
       </c>
@@ -2241,7 +2241,7 @@
       </c>
       <c r="M37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="n">
         <v>1</v>
       </c>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="M38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="n">
         <v>1</v>
       </c>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="M39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="n">
         <v>1</v>
       </c>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="M40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="n">
         <v>1</v>
       </c>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="M41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="n">
         <v>1</v>
       </c>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="M42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="n">
         <v>1</v>
       </c>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="n">
         <v>1</v>
       </c>
@@ -2514,7 +2514,7 @@
       </c>
       <c r="M44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="n">
         <v>1</v>
       </c>
@@ -2553,7 +2553,7 @@
       </c>
       <c r="M45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="n">
         <v>1</v>
       </c>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="M46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="n">
         <v>2</v>
       </c>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="M47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="n">
         <v>2</v>
       </c>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="M48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="n">
         <v>2</v>
       </c>
@@ -2709,7 +2709,7 @@
       </c>
       <c r="M49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="n">
         <v>2</v>
       </c>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="M50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="n">
         <v>2</v>
       </c>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="M51" s="3"/>
     </row>
-    <row r="52" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" s="5" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="n">
         <v>2</v>
       </c>
@@ -2836,7 +2836,7 @@
       <c r="V52" s="1"/>
       <c r="W52" s="1"/>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="n">
         <v>2</v>
       </c>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="M53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="1" t="n">
         <v>2</v>
       </c>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="M54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="1" t="n">
         <v>2</v>
       </c>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="M55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="n">
         <v>2</v>
       </c>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="M56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="n">
         <v>2</v>
       </c>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="M57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="n">
         <v>2</v>
       </c>
@@ -3070,7 +3070,7 @@
       </c>
       <c r="M58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="n">
         <v>2</v>
       </c>
@@ -3109,7 +3109,7 @@
       </c>
       <c r="M59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="n">
         <v>2</v>
       </c>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="M60" s="3"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="n">
         <v>2</v>
       </c>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="M61" s="3"/>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="n">
         <v>2</v>
       </c>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="M62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="n">
         <v>2</v>
       </c>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="M63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="n">
         <v>2</v>
       </c>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M64" s="6"/>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="n">
         <v>2</v>
       </c>
@@ -3343,7 +3343,7 @@
       </c>
       <c r="M65" s="6"/>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="n">
         <v>2</v>
       </c>
@@ -3382,7 +3382,7 @@
       </c>
       <c r="M66" s="6"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="n">
         <v>2</v>
       </c>
@@ -3421,7 +3421,7 @@
       </c>
       <c r="M67" s="6"/>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="n">
         <v>2</v>
       </c>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="M68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="n">
         <v>2</v>
       </c>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="M69" s="3"/>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="n">
         <v>2</v>
       </c>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="M70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="n">
         <v>2</v>
       </c>
@@ -3577,7 +3577,7 @@
       </c>
       <c r="M71" s="3"/>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="n">
         <v>2</v>
       </c>
@@ -3616,7 +3616,7 @@
       </c>
       <c r="M72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="n">
         <v>2</v>
       </c>
@@ -3655,7 +3655,7 @@
       </c>
       <c r="M73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="n">
         <v>2</v>
       </c>
@@ -3694,7 +3694,7 @@
       </c>
       <c r="M74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="n">
         <v>2</v>
       </c>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="M75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="n">
         <v>3</v>
       </c>
@@ -3772,7 +3772,7 @@
       </c>
       <c r="M76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="n">
         <v>3</v>
       </c>
@@ -3811,7 +3811,7 @@
       </c>
       <c r="M77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="n">
         <v>3</v>
       </c>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="M78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="n">
         <v>3</v>
       </c>
@@ -3889,7 +3889,7 @@
       </c>
       <c r="M79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="n">
         <v>3</v>
       </c>
@@ -3928,7 +3928,7 @@
       </c>
       <c r="M80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="n">
         <v>3</v>
       </c>
@@ -3967,7 +3967,7 @@
       </c>
       <c r="M81" s="3"/>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="n">
         <v>3</v>
       </c>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="M82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="n">
         <v>3</v>
       </c>
@@ -4045,7 +4045,7 @@
       </c>
       <c r="M83" s="3"/>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="n">
         <v>3</v>
       </c>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="M84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="n">
         <v>3</v>
       </c>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="M85" s="3"/>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="n">
         <v>3</v>
       </c>
@@ -4162,7 +4162,7 @@
       </c>
       <c r="M86" s="3"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="n">
         <v>3</v>
       </c>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="M87" s="3"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="n">
         <v>3</v>
       </c>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="M88" s="3"/>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="n">
         <v>3</v>
       </c>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="n">
         <v>3</v>
       </c>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="M90" s="3"/>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="n">
         <v>3</v>
       </c>
@@ -4357,7 +4357,7 @@
       </c>
       <c r="M91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="n">
         <v>3</v>
       </c>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="M92" s="3"/>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="1" t="n">
         <v>3</v>
       </c>
@@ -4435,7 +4435,7 @@
       </c>
       <c r="M93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="n">
         <v>3</v>
       </c>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="M94" s="3"/>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="n">
         <v>3</v>
       </c>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="M95" s="3"/>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="n">
         <v>3</v>
       </c>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="M96" s="3"/>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="1" t="n">
         <v>3</v>
       </c>
@@ -4591,7 +4591,7 @@
       </c>
       <c r="M97" s="3"/>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="n">
         <v>3</v>
       </c>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="M98" s="3"/>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="n">
         <v>3</v>
       </c>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="M99" s="3"/>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="n">
         <v>3</v>
       </c>
@@ -4708,7 +4708,7 @@
       </c>
       <c r="M100" s="3"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="n">
         <v>3</v>
       </c>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="M101" s="3"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="n">
         <v>3</v>
       </c>
@@ -4786,7 +4786,7 @@
       </c>
       <c r="M102" s="3"/>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="15.75" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="n">
         <v>3</v>
       </c>
@@ -4825,7 +4825,7 @@
       </c>
       <c r="M103" s="3"/>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="n">
         <v>3</v>
       </c>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="M104" s="3"/>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="1" t="n">
         <v>3</v>
       </c>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="M105" s="3"/>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="n">
         <v>3</v>
       </c>
@@ -4942,7 +4942,7 @@
       </c>
       <c r="M106" s="3"/>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="n">
         <v>3</v>
       </c>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="M107" s="3"/>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="n">
         <v>3</v>
       </c>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="M108" s="3"/>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="n">
         <v>3</v>
       </c>
@@ -5059,7 +5059,7 @@
       </c>
       <c r="M109" s="3"/>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="n">
         <v>3</v>
       </c>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="M110" s="3"/>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="n">
         <v>3</v>
       </c>
@@ -5137,7 +5137,7 @@
       </c>
       <c r="M111" s="3"/>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="n">
         <v>3</v>
       </c>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="M112" s="3"/>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="n">
         <v>3</v>
       </c>
@@ -5215,7 +5215,7 @@
       </c>
       <c r="M113" s="3"/>
     </row>
-    <row r="114" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="n">
         <v>3</v>
       </c>
@@ -5264,7 +5264,7 @@
       <c r="V114" s="1"/>
       <c r="W114" s="1"/>
     </row>
-    <row r="115" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="1" t="n">
         <v>3</v>
       </c>
@@ -5313,7 +5313,7 @@
       <c r="V115" s="1"/>
       <c r="W115" s="1"/>
     </row>
-    <row r="116" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="n">
         <v>3</v>
       </c>
@@ -5362,7 +5362,7 @@
       <c r="V116" s="1"/>
       <c r="W116" s="1"/>
     </row>
-    <row r="117" s="4" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" s="4" customFormat="true" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="n">
         <v>3</v>
       </c>
@@ -5411,7 +5411,7 @@
       <c r="V117" s="1"/>
       <c r="W117" s="1"/>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="n">
         <v>3</v>
       </c>
@@ -5450,7 +5450,7 @@
       </c>
       <c r="M118" s="3"/>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="n">
         <v>3</v>
       </c>
@@ -5489,7 +5489,7 @@
       </c>
       <c r="M119" s="3"/>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="n">
         <v>3</v>
       </c>
@@ -5528,7 +5528,7 @@
       </c>
       <c r="M120" s="3"/>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="n">
         <v>3</v>
       </c>
@@ -5567,7 +5567,7 @@
       </c>
       <c r="M121" s="3"/>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="n">
         <v>3</v>
       </c>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="M122" s="3"/>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="n">
         <v>3</v>
       </c>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="M123" s="3"/>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="n">
         <v>3</v>
       </c>
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M124" s="3"/>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="n">
         <v>3</v>
       </c>
@@ -5723,7 +5723,7 @@
       </c>
       <c r="M125" s="3"/>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="n">
         <v>3</v>
       </c>
@@ -5762,7 +5762,7 @@
       </c>
       <c r="M126" s="3"/>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="n">
         <v>3</v>
       </c>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="M127" s="3"/>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="15" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="n">
         <v>3</v>
       </c>
@@ -6779,19 +6779,19 @@
     </row>
     <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B152" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="F152" s="1" t="n">
         <v>1</v>
@@ -6812,245 +6812,245 @@
         <v>0</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="M152" s="3"/>
     </row>
     <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B153" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F153" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G153" s="1" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="H153" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I153" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J153" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K153" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L153" s="1" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="M153" s="3"/>
     </row>
     <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B154" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F154" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G154" s="1" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H154" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I154" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J154" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K154" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>40</v>
+        <v>107</v>
       </c>
       <c r="M154" s="3"/>
     </row>
     <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B155" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F155" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G155" s="1" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="H155" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I155" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J155" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K155" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="M155" s="3"/>
     </row>
     <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B156" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="F156" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156" s="1" t="n">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="H156" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I156" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J156" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K156" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="M156" s="3"/>
     </row>
     <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="1" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>52</v>
+        <v>22</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="F157" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G157" s="1" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="H157" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I157" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J157" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K157" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I157" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J157" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="K157" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L157" s="1" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M157" s="3"/>
     </row>
     <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E158" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G158" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="H158" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I158" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J158" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K158" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B158" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C158" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D158" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="E158" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="F158" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G158" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="H158" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I158" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J158" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="K158" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="L158" s="1" t="s">
-        <v>105</v>
+        <v>49</v>
       </c>
       <c r="M158" s="3"/>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="1" t="n">
         <v>5</v>
       </c>
@@ -7067,29 +7067,29 @@
         <v>52</v>
       </c>
       <c r="F159" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G159" s="1" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I159" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J159" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="K159" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L159" s="1" t="s">
-        <v>105</v>
+        <v>39</v>
       </c>
       <c r="M159" s="3"/>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="1" t="n">
         <v>5</v>
       </c>
@@ -7100,35 +7100,35 @@
         <v>52</v>
       </c>
       <c r="D160" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E160" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E160" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="F160" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G160" s="1" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I160" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J160" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K160" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L160" s="1" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="M160" s="3"/>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="1" t="n">
         <v>5</v>
       </c>
@@ -7145,199 +7145,199 @@
         <v>52</v>
       </c>
       <c r="F161" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G161" s="1" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="I161" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J161" s="1" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="K161" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L161" s="1" t="s">
-        <v>105</v>
+        <v>40</v>
       </c>
       <c r="M161" s="3"/>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B162" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F162" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G162" s="1" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I162" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J162" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K162" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L162" s="1" t="s">
-        <v>106</v>
+        <v>39</v>
       </c>
       <c r="M162" s="3"/>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B163" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F163" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G163" s="1" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I163" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J163" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K163" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L163" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M163" s="3"/>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B164" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F164" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G164" s="1" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I164" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J164" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K164" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L164" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="M164" s="3"/>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F165" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G165" s="1" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I165" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J165" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K165" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L165" s="1" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="M165" s="3"/>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B166" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="F166" s="1" t="n">
         <v>2</v>
@@ -7346,115 +7346,115 @@
         <v>32</v>
       </c>
       <c r="H166" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I166" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J166" s="1" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K166" s="1" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L166" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="M166" s="3"/>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B167" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C167" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="F167" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G167" s="1" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="H167" s="1" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I167" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J167" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="K167" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L167" s="1" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="M167" s="3"/>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B168" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F168" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G168" s="1" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="H168" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I168" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J168" s="1" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K168" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L168" s="1" t="s">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="M168" s="3"/>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B169" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F169" s="1" t="n">
         <v>1</v>
@@ -7463,179 +7463,179 @@
         <v>9</v>
       </c>
       <c r="H169" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I169" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J169" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K169" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L169" s="1" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="M169" s="3"/>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B170" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F170" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G170" s="1" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H170" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I170" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J170" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K170" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L170" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="M170" s="3"/>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B171" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F171" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G171" s="1" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H171" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I171" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J171" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K171" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="M171" s="3"/>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B172" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F172" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G172" s="1" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="H172" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I172" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J172" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K172" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L172" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="M172" s="3"/>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>51</v>
+        <v>13</v>
       </c>
       <c r="F173" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G173" s="1" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="H173" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I173" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J173" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K173" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K173" s="1" t="n">
-        <v>3</v>
-      </c>
       <c r="L173" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="M173" s="3"/>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="1" t="n">
         <v>5</v>
       </c>
@@ -7646,728 +7646,1268 @@
         <v>51</v>
       </c>
       <c r="D174" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E174" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E174" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="F174" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G174" s="1" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="H174" s="1" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I174" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J174" s="1" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K174" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L174" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M174" s="3"/>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B175" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F175" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G175" s="1" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H175" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I175" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J175" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K175" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="M175" s="3"/>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B176" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="F176" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G176" s="1" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H176" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I176" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J176" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K176" s="1" t="n">
         <v>1</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="M176" s="3"/>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B177" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F177" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G177" s="1" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H177" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I177" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J177" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K177" s="1" t="n">
         <v>2</v>
       </c>
       <c r="L177" s="1" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="M177" s="3"/>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B178" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="F178" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G178" s="1" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I178" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J178" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K178" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L178" s="1" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="M178" s="3"/>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B179" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C179" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="F179" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G179" s="1" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I179" s="1" t="n">
         <v>3</v>
       </c>
       <c r="J179" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K179" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L179" s="1" t="s">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="M179" s="3"/>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B180" s="1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="F180" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G180" s="1" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H180" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I180" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J180" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K180" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L180" s="1" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="M180" s="3"/>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B181" s="1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="F181" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G181" s="1" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="H181" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I181" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J181" s="1" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K181" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L181" s="1" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="M181" s="3"/>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B182" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F182" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G182" s="1" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H182" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I182" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J182" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K182" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L182" s="1" t="s">
-        <v>83</v>
+        <v>20</v>
       </c>
       <c r="M182" s="3"/>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B183" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="F183" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G183" s="1" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="H183" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I183" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J183" s="1" t="n">
         <v>1</v>
       </c>
       <c r="K183" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L183" s="1" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="M183" s="3"/>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B184" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F184" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G184" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H184" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I184" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J184" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K184" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="M184" s="3"/>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B185" s="1" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F185" s="1" t="n">
         <v>2</v>
       </c>
       <c r="G185" s="1" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="H185" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I185" s="1" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J185" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K185" s="1" t="n">
         <v>3</v>
       </c>
       <c r="L185" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="M185" s="3"/>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B186" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C186" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F186" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G186" s="1" t="n">
-        <v>2</v>
+        <v>38</v>
       </c>
       <c r="H186" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I186" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J186" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K186" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="M186" s="3"/>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B187" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F187" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G187" s="1" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I187" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J187" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K187" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L187" s="1" t="s">
-        <v>101</v>
+        <v>83</v>
       </c>
       <c r="M187" s="3"/>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="F188" s="1" t="n">
         <v>1</v>
       </c>
       <c r="G188" s="1" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H188" s="1" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I188" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J188" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K188" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L188" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="M188" s="3"/>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="F189" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G189" s="1" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H189" s="1" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I189" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J189" s="1" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K189" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L189" s="1" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="M189" s="3"/>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="1" t="n">
         <v>5</v>
       </c>
       <c r="B190" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E190" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F190" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G190" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="H190" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I190" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J190" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K190" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L190" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="M190" s="3"/>
+    </row>
+    <row r="191" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E191" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F191" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G191" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="H191" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I191" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J191" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K191" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L191" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="M191" s="3"/>
+    </row>
+    <row r="192" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E192" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F192" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G192" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="H192" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I192" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J192" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K192" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L192" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="M192" s="3"/>
+    </row>
+    <row r="193" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B193" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C190" s="1" t="s">
+      <c r="C193" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D190" s="1" t="s">
+      <c r="D193" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E190" s="1" t="s">
+      <c r="E193" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F190" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="G190" s="1" t="n">
+      <c r="F193" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G193" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H193" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I193" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J193" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K193" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L193" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M193" s="3"/>
+    </row>
+    <row r="194" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E194" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F194" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G194" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="H194" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I194" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J194" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K194" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L194" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="M194" s="3"/>
+    </row>
+    <row r="195" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E195" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F195" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G195" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="H195" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I195" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J195" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K195" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L195" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="M195" s="3"/>
+    </row>
+    <row r="196" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E196" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F196" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G196" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="H196" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I196" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J196" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K196" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L196" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="M196" s="3"/>
+    </row>
+    <row r="197" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E197" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F197" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G197" s="1" t="n">
         <v>40</v>
       </c>
-      <c r="H190" s="1" t="n">
+      <c r="H197" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="I190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J190" s="1" t="n">
+      <c r="I197" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J197" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="K190" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L190" s="1" t="s">
+      <c r="K197" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L197" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="M190" s="3"/>
-    </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M191" s="3"/>
-    </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M192" s="3"/>
-    </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M193" s="3"/>
-    </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M194" s="3"/>
-    </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M195" s="3"/>
-    </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="M196" s="3"/>
-    </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M197" s="3"/>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M198" s="3"/>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M199" s="3"/>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M200" s="3"/>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M201" s="3"/>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M202" s="3"/>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M203" s="3"/>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M204" s="3"/>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M205" s="3"/>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="M206" s="3"/>
     </row>
     <row r="207" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E207" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F207" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G207" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="H207" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I207" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J207" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K207" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L207" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="M207" s="3"/>
     </row>
     <row r="208" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E208" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F208" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G208" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="H208" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I208" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J208" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K208" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L208" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="M208" s="3"/>
     </row>
     <row r="209" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E209" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F209" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G209" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="H209" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I209" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J209" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K209" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L209" s="1" t="s">
+        <v>56</v>
+      </c>
       <c r="M209" s="3"/>
     </row>
     <row r="210" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E210" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F210" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G210" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="H210" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I210" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J210" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K210" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L210" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="M210" s="3"/>
     </row>
     <row r="211" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E211" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F211" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G211" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="H211" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I211" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J211" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="K211" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L211" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="M211" s="3"/>
     </row>
     <row r="212" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E212" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F212" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G212" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="H212" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I212" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J212" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K212" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L212" s="1" t="s">
+        <v>65</v>
+      </c>
       <c r="M212" s="3"/>
     </row>
     <row r="213" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E213" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F213" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G213" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="H213" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I213" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J213" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K213" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L213" s="1" t="s">
+        <v>68</v>
+      </c>
       <c r="M213" s="3"/>
     </row>
     <row r="214" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F214" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G214" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="H214" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I214" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="J214" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K214" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L214" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="M214" s="3"/>
     </row>
     <row r="215" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -10729,7 +11269,13 @@
       <c r="M1000" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M206"/>
+  <autoFilter ref="A1:M206">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="4"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation allowBlank="true" error="Choisir une origine dans la liste." errorStyle="stop" errorTitle="Origine inconnue" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="false" sqref="M2:M1000" type="list">
       <formula1>"attaque placée,attaque rapide,transition off,corner,touche off,touche def,coup franc,jet franc,power play,penalty,csc"</formula1>
@@ -10809,7 +11355,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10850,7 +11396,7 @@
         <v>39</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -10901,7 +11447,7 @@
         <v>40</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -10952,7 +11498,7 @@
         <v>39</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -11003,7 +11549,7 @@
         <v>40</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -11054,7 +11600,7 @@
         <v>39</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -11105,7 +11651,7 @@
         <v>39</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -11156,7 +11702,7 @@
         <v>39</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -11207,7 +11753,7 @@
         <v>40</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -11258,7 +11804,7 @@
         <v>91</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -11309,7 +11855,7 @@
         <v>39</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -11360,7 +11906,7 @@
         <v>91</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -11411,7 +11957,7 @@
         <v>92</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -11462,7 +12008,7 @@
         <v>39</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -11513,7 +12059,7 @@
         <v>92</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -11564,7 +12110,7 @@
         <v>40</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -11615,7 +12161,7 @@
         <v>93</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -11666,7 +12212,7 @@
         <v>93</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -11717,7 +12263,7 @@
         <v>104</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -11768,7 +12314,7 @@
         <v>39</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -11819,7 +12365,7 @@
         <v>40</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -11867,10 +12413,10 @@
         <v>1</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -11921,7 +12467,7 @@
         <v>129</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -11969,10 +12515,10 @@
         <v>2</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -12020,10 +12566,10 @@
         <v>2</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -12074,7 +12620,7 @@
         <v>39</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
@@ -12122,10 +12668,10 @@
         <v>2</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="M27" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
@@ -12834,7 +13380,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
@@ -12885,7 +13431,7 @@
         <v>44</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -12936,7 +13482,7 @@
         <v>46</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -12987,7 +13533,7 @@
         <v>47</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -13038,7 +13584,7 @@
         <v>48</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -13089,7 +13635,7 @@
         <v>48</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -13140,7 +13686,7 @@
         <v>46</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -13191,7 +13737,7 @@
         <v>48</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -13242,7 +13788,7 @@
         <v>48</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -13293,7 +13839,7 @@
         <v>47</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -13344,7 +13890,7 @@
         <v>95</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -13395,7 +13941,7 @@
         <v>48</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -13446,7 +13992,7 @@
         <v>48</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -13497,7 +14043,7 @@
         <v>95</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -13548,7 +14094,7 @@
         <v>97</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -13599,7 +14145,7 @@
         <v>97</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
@@ -13650,7 +14196,7 @@
         <v>99</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
@@ -13701,7 +14247,7 @@
         <v>49</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -13752,7 +14298,7 @@
         <v>46</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -13854,7 +14400,7 @@
         <v>46</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -13905,7 +14451,7 @@
         <v>48</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -14086,7 +14632,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14127,7 +14673,7 @@
         <v>54</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -14178,7 +14724,7 @@
         <v>55</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -14229,7 +14775,7 @@
         <v>54</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -14280,7 +14826,7 @@
         <v>73</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -14331,7 +14877,7 @@
         <v>74</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -14382,7 +14928,7 @@
         <v>54</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -14433,7 +14979,7 @@
         <v>75</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -14484,7 +15030,7 @@
         <v>76</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -14535,7 +15081,7 @@
         <v>78</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -14586,7 +15132,7 @@
         <v>73</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -14637,7 +15183,7 @@
         <v>78</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -14688,7 +15234,7 @@
         <v>73</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -14739,7 +15285,7 @@
         <v>75</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -14790,7 +15336,7 @@
         <v>78</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -14838,7 +15384,7 @@
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="M16" s="3" t="s">
         <v>126</v>
@@ -14889,10 +15435,10 @@
         <v>2</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -14943,7 +15489,7 @@
         <v>74</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -15165,7 +15711,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15206,7 +15752,7 @@
         <v>45</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15247,7 +15793,7 @@
         <v>49</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15288,7 +15834,7 @@
         <v>50</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15329,7 +15875,7 @@
         <v>45</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15370,7 +15916,7 @@
         <v>82</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15411,7 +15957,7 @@
         <v>84</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15452,7 +15998,7 @@
         <v>86</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15493,7 +16039,7 @@
         <v>87</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" s="5" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -15534,7 +16080,7 @@
         <v>102</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -15585,7 +16131,7 @@
         <v>45</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -15636,7 +16182,7 @@
         <v>84</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -15687,7 +16233,7 @@
         <v>102</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -15795,7 +16341,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -15846,7 +16392,7 @@
         <v>32</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -15897,7 +16443,7 @@
         <v>33</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -15948,7 +16494,7 @@
         <v>34</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -15999,7 +16545,7 @@
         <v>35</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -16050,7 +16596,7 @@
         <v>36</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -16101,7 +16647,7 @@
         <v>69</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -16152,7 +16698,7 @@
         <v>70</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -16203,7 +16749,7 @@
         <v>70</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -16254,7 +16800,7 @@
         <v>35</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -16305,7 +16851,7 @@
         <v>90</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -16356,7 +16902,7 @@
         <v>70</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16397,7 +16943,7 @@
         <v>34</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -16448,7 +16994,7 @@
         <v>103</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -16499,7 +17045,7 @@
         <v>34</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -16550,7 +17096,7 @@
         <v>32</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -16862,7 +17408,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16903,7 +17449,7 @@
         <v>65</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -16954,7 +17500,7 @@
         <v>66</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -17005,7 +17551,7 @@
         <v>68</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -17056,7 +17602,7 @@
         <v>77</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" s="5" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -17097,7 +17643,7 @@
         <v>65</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -17148,7 +17694,7 @@
         <v>65</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -17199,7 +17745,7 @@
         <v>68</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -17250,7 +17796,7 @@
         <v>66</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -17298,10 +17844,10 @@
         <v>1</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -17349,10 +17895,10 @@
         <v>3</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -17614,7 +18160,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17655,7 +18201,7 @@
         <v>41</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -17706,7 +18252,7 @@
         <v>58</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -17757,7 +18303,7 @@
         <v>59</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -17808,7 +18354,7 @@
         <v>49</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -17859,7 +18405,7 @@
         <v>58</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -17910,7 +18456,7 @@
         <v>80</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -17961,7 +18507,7 @@
         <v>81</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -18012,7 +18558,7 @@
         <v>58</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -18063,7 +18609,7 @@
         <v>59</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -18114,7 +18660,7 @@
         <v>83</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -18165,7 +18711,7 @@
         <v>80</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -18216,7 +18762,7 @@
         <v>85</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -18267,7 +18813,7 @@
         <v>59</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -18318,7 +18864,7 @@
         <v>83</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -18369,7 +18915,7 @@
         <v>83</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -18420,7 +18966,7 @@
         <v>80</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -18634,7 +19180,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18675,7 +19221,7 @@
         <v>25</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -18726,7 +19272,7 @@
         <v>26</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -18777,7 +19323,7 @@
         <v>27</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -18828,7 +19374,7 @@
         <v>26</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -18879,7 +19425,7 @@
         <v>28</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -18930,7 +19476,7 @@
         <v>25</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -18981,7 +19527,7 @@
         <v>26</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -19032,7 +19578,7 @@
         <v>60</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -19083,7 +19629,7 @@
         <v>61</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -19134,7 +19680,7 @@
         <v>25</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -19185,7 +19731,7 @@
         <v>27</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -19236,7 +19782,7 @@
         <v>88</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -19287,7 +19833,7 @@
         <v>89</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -19338,7 +19884,7 @@
         <v>26</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -19386,10 +19932,10 @@
         <v>1</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -19440,7 +19986,7 @@
         <v>60</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -19491,7 +20037,7 @@
         <v>89</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
@@ -19542,7 +20088,7 @@
         <v>49</v>
       </c>
       <c r="M19" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
@@ -19593,7 +20139,7 @@
         <v>49</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -19644,7 +20190,7 @@
         <v>60</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -19695,7 +20241,7 @@
         <v>60</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -19746,7 +20292,7 @@
         <v>61</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -19794,10 +20340,10 @@
         <v>3</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -19845,10 +20391,10 @@
         <v>3</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -20261,7 +20807,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20302,7 +20848,7 @@
         <v>14</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20343,7 +20889,7 @@
         <v>15</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20384,7 +20930,7 @@
         <v>16</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20425,7 +20971,7 @@
         <v>18</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20466,7 +21012,7 @@
         <v>14</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20507,7 +21053,7 @@
         <v>20</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20548,7 +21094,7 @@
         <v>21</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20589,7 +21135,7 @@
         <v>14</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -20640,7 +21186,7 @@
         <v>71</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -20691,7 +21237,7 @@
         <v>14</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -20742,7 +21288,7 @@
         <v>72</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -20793,7 +21339,7 @@
         <v>18</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -20844,7 +21390,7 @@
         <v>14</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -20895,7 +21441,7 @@
         <v>15</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -20946,7 +21492,7 @@
         <v>18</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -20997,7 +21543,7 @@
         <v>72</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -21048,7 +21594,7 @@
         <v>14</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
@@ -21099,7 +21645,7 @@
         <v>98</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -21150,7 +21696,7 @@
         <v>98</v>
       </c>
       <c r="M20" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
@@ -21201,7 +21747,7 @@
         <v>16</v>
       </c>
       <c r="M21" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N21" s="1"/>
       <c r="O21" s="1"/>
@@ -21252,7 +21798,7 @@
         <v>18</v>
       </c>
       <c r="M22" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N22" s="1"/>
       <c r="O22" s="1"/>
@@ -21303,7 +21849,7 @@
         <v>20</v>
       </c>
       <c r="M23" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N23" s="1"/>
       <c r="O23" s="1"/>
@@ -21354,7 +21900,7 @@
         <v>15</v>
       </c>
       <c r="M24" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
@@ -21405,7 +21951,7 @@
         <v>16</v>
       </c>
       <c r="M25" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -23219,7 +23765,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23260,7 +23806,7 @@
         <v>53</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -23311,7 +23857,7 @@
         <v>56</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -23362,7 +23908,7 @@
         <v>56</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -23413,7 +23959,7 @@
         <v>57</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -23464,7 +24010,7 @@
         <v>62</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -23515,7 +24061,7 @@
         <v>56</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -23566,7 +24112,7 @@
         <v>53</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -23617,7 +24163,7 @@
         <v>79</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -23668,7 +24214,7 @@
         <v>56</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -23719,7 +24265,7 @@
         <v>56</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -23770,7 +24316,7 @@
         <v>56</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -23821,7 +24367,7 @@
         <v>62</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -23872,7 +24418,7 @@
         <v>62</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -23923,7 +24469,7 @@
         <v>53</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -24167,7 +24713,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
@@ -24218,7 +24764,7 @@
         <v>17</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24259,7 +24805,7 @@
         <v>19</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
@@ -24310,7 +24856,7 @@
         <v>67</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
@@ -24358,10 +24904,10 @@
         <v>0</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
@@ -24412,7 +24958,7 @@
         <v>106</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -24463,7 +25009,7 @@
         <v>106</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -24514,7 +25060,7 @@
         <v>106</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -24565,7 +25111,7 @@
         <v>67</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -26199,7 +26745,7 @@
         <v>11</v>
       </c>
       <c r="M1" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26240,7 +26786,7 @@
         <v>24</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26281,7 +26827,7 @@
         <v>29</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26322,7 +26868,7 @@
         <v>24</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26363,7 +26909,7 @@
         <v>29</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" s="5" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26404,7 +26950,7 @@
         <v>63</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
@@ -26455,7 +27001,7 @@
         <v>64</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
@@ -26506,7 +27052,7 @@
         <v>29</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
@@ -26557,7 +27103,7 @@
         <v>94</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
@@ -26608,7 +27154,7 @@
         <v>96</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
@@ -26659,7 +27205,7 @@
         <v>63</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
@@ -26710,7 +27256,7 @@
         <v>100</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
@@ -26761,7 +27307,7 @@
         <v>101</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
@@ -26812,7 +27358,7 @@
         <v>94</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
@@ -26863,7 +27409,7 @@
         <v>127</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
@@ -26914,7 +27460,7 @@
         <v>29</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -26962,10 +27508,10 @@
         <v>0</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="M17" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
@@ -27016,7 +27562,7 @@
         <v>100</v>
       </c>
       <c r="M18" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
